--- a/grupos/5BLCM - Estadisticos 20231.xlsx
+++ b/grupos/5BLCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="156">
   <si>
     <t>Materia</t>
   </si>
@@ -3678,13 +3678,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>47</v>
@@ -3693,22 +3693,25 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3722,48 +3725,57 @@
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="S2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -3777,7 +3789,7 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -3795,7 +3807,7 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -3812,8 +3824,17 @@
       <c r="P4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -3827,17 +3848,17 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G5">
+        <v>96.7</v>
+      </c>
+      <c r="H5">
         <v>93.3</v>
       </c>
-      <c r="H5">
-        <v>100</v>
-      </c>
       <c r="I5">
         <v>100</v>
       </c>
@@ -3845,25 +3866,34 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L5">
+        <v>100</v>
+      </c>
+      <c r="M5">
+        <v>96.7</v>
+      </c>
+      <c r="N5">
         <v>93.3</v>
       </c>
-      <c r="M5">
-        <v>100</v>
-      </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>100</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>100</v>
+      </c>
+      <c r="S5">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -3877,7 +3907,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -3895,7 +3925,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3912,8 +3942,17 @@
       <c r="P6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>100</v>
+      </c>
+      <c r="S6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -3927,43 +3966,52 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G7">
+        <v>96.7</v>
+      </c>
+      <c r="H7">
         <v>93.3</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>95</v>
       </c>
-      <c r="I7">
-        <v>100</v>
-      </c>
       <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L7">
+        <v>100</v>
+      </c>
+      <c r="M7">
+        <v>96.7</v>
+      </c>
+      <c r="N7">
         <v>93.3</v>
       </c>
-      <c r="M7">
+      <c r="O7">
         <v>95</v>
       </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
-      <c r="O7">
-        <v>100</v>
-      </c>
       <c r="P7">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>100</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>100</v>
+      </c>
+      <c r="S7">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -3977,16 +4025,16 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>86.7</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -3995,25 +4043,34 @@
         <v>100</v>
       </c>
       <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>100</v>
+      </c>
+      <c r="M8">
         <v>86.7</v>
       </c>
-      <c r="L8">
+      <c r="N8">
         <v>86.7</v>
       </c>
-      <c r="M8">
-        <v>100</v>
-      </c>
-      <c r="N8">
-        <v>100</v>
-      </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
+        <v>100</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>100</v>
+      </c>
+      <c r="S8">
         <v>86.7</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -4027,16 +4084,16 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G9">
         <v>96.7</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -4045,25 +4102,34 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O9">
         <v>100</v>
       </c>
       <c r="P9">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>100</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>100</v>
+      </c>
+      <c r="S9">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -4077,7 +4143,7 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -4095,7 +4161,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -4112,8 +4178,17 @@
       <c r="P10">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>100</v>
+      </c>
+      <c r="S10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -4127,43 +4202,52 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G11">
+        <v>96.7</v>
+      </c>
+      <c r="H11">
         <v>93.3</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>85</v>
       </c>
-      <c r="I11">
-        <v>100</v>
-      </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L11">
+        <v>100</v>
+      </c>
+      <c r="M11">
+        <v>96.7</v>
+      </c>
+      <c r="N11">
         <v>93.3</v>
       </c>
-      <c r="M11">
+      <c r="O11">
         <v>85</v>
       </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
-      <c r="O11">
-        <v>100</v>
-      </c>
       <c r="P11">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>100</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -4177,7 +4261,7 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -4195,7 +4279,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -4212,8 +4296,17 @@
       <c r="P12">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -4227,16 +4320,16 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G13">
         <v>96.7</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -4245,25 +4338,34 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>100</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>100</v>
+      </c>
+      <c r="S13">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -4277,7 +4379,7 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -4295,7 +4397,7 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -4312,8 +4414,17 @@
       <c r="P14">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -4327,16 +4438,16 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>96.7</v>
       </c>
       <c r="H15">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I15">
         <v>100</v>
@@ -4345,25 +4456,34 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O15">
         <v>100</v>
       </c>
       <c r="P15">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+        <v>100</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -4377,7 +4497,7 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -4395,7 +4515,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -4412,8 +4532,17 @@
       <c r="P16">
         <v>100</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -4427,43 +4556,52 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>96.7</v>
       </c>
       <c r="H17">
+        <v>96.7</v>
+      </c>
+      <c r="I17">
         <v>95</v>
       </c>
-      <c r="I17">
-        <v>100</v>
-      </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M17">
+        <v>96.7</v>
+      </c>
+      <c r="N17">
+        <v>96.7</v>
+      </c>
+      <c r="O17">
         <v>95</v>
       </c>
-      <c r="N17">
-        <v>100</v>
-      </c>
-      <c r="O17">
-        <v>100</v>
-      </c>
       <c r="P17">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
+        <v>100</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>100</v>
+      </c>
+      <c r="S17">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -4477,43 +4615,52 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18">
         <v>93.3</v>
       </c>
-      <c r="G18">
-        <v>96.7</v>
-      </c>
       <c r="H18">
+        <v>96.7</v>
+      </c>
+      <c r="I18">
         <v>95</v>
       </c>
-      <c r="I18">
-        <v>100</v>
-      </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>100</v>
+      </c>
+      <c r="M18">
         <v>93.3</v>
       </c>
-      <c r="L18">
-        <v>96.7</v>
-      </c>
-      <c r="M18">
+      <c r="N18">
+        <v>96.7</v>
+      </c>
+      <c r="O18">
         <v>95</v>
       </c>
-      <c r="N18">
-        <v>100</v>
-      </c>
-      <c r="O18">
-        <v>100</v>
-      </c>
       <c r="P18">
+        <v>100</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>100</v>
+      </c>
+      <c r="S18">
         <v>93.3</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -4527,16 +4674,16 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19">
+        <v>100</v>
+      </c>
+      <c r="G19">
         <v>93.3</v>
       </c>
-      <c r="G19">
-        <v>96.7</v>
-      </c>
       <c r="H19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -4545,25 +4692,34 @@
         <v>100</v>
       </c>
       <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>100</v>
+      </c>
+      <c r="M19">
         <v>93.3</v>
       </c>
-      <c r="L19">
-        <v>96.7</v>
-      </c>
-      <c r="M19">
-        <v>100</v>
-      </c>
       <c r="N19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19">
+        <v>100</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>100</v>
+      </c>
+      <c r="S19">
         <v>93.3</v>
       </c>
     </row>
-    <row r="20" spans="1:16">
+    <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -4577,16 +4733,16 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>96.7</v>
       </c>
       <c r="H20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -4595,25 +4751,34 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
+        <v>100</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>100</v>
+      </c>
+      <c r="S20">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -4627,43 +4792,52 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F21">
+        <v>100</v>
+      </c>
+      <c r="G21">
         <v>90</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>86.7</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>90</v>
       </c>
-      <c r="I21">
-        <v>100</v>
-      </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L21">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="M21">
         <v>90</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P21">
+        <v>100</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -4677,17 +4851,17 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>100</v>
       </c>
       <c r="G22">
+        <v>100</v>
+      </c>
+      <c r="H22">
         <v>93.3</v>
       </c>
-      <c r="H22">
-        <v>100</v>
-      </c>
       <c r="I22">
         <v>100</v>
       </c>
@@ -4695,25 +4869,34 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22">
+        <v>100</v>
+      </c>
+      <c r="M22">
+        <v>100</v>
+      </c>
+      <c r="N22">
         <v>93.3</v>
       </c>
-      <c r="M22">
-        <v>100</v>
-      </c>
-      <c r="N22">
-        <v>100</v>
-      </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -4727,16 +4910,16 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>96.7</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I23">
         <v>100</v>
@@ -4745,25 +4928,34 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
+        <v>100</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>100</v>
+      </c>
+      <c r="S23">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -4777,16 +4969,16 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24">
+        <v>100</v>
+      </c>
+      <c r="G24">
         <v>93.3</v>
       </c>
-      <c r="G24">
-        <v>96.7</v>
-      </c>
       <c r="H24">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I24">
         <v>100</v>
@@ -4795,25 +4987,34 @@
         <v>100</v>
       </c>
       <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>100</v>
+      </c>
+      <c r="M24">
         <v>93.3</v>
       </c>
-      <c r="L24">
-        <v>96.7</v>
-      </c>
-      <c r="M24">
-        <v>100</v>
-      </c>
       <c r="N24">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24">
+        <v>100</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>100</v>
+      </c>
+      <c r="S24">
         <v>93.3</v>
       </c>
     </row>
-    <row r="25" spans="1:16">
+    <row r="25" spans="1:19">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
@@ -4827,16 +5028,16 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>96.7</v>
       </c>
       <c r="H25">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I25">
         <v>100</v>
@@ -4845,25 +5046,34 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
+        <v>100</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>100</v>
+      </c>
+      <c r="S25">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -4877,7 +5087,7 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -4895,7 +5105,7 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -4912,8 +5122,17 @@
       <c r="P26">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>100</v>
+      </c>
+      <c r="S26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -4927,16 +5146,16 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27">
+        <v>100</v>
+      </c>
+      <c r="G27">
         <v>93.3</v>
       </c>
-      <c r="G27">
-        <v>96.7</v>
-      </c>
       <c r="H27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -4945,25 +5164,34 @@
         <v>100</v>
       </c>
       <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>100</v>
+      </c>
+      <c r="M27">
         <v>93.3</v>
       </c>
-      <c r="L27">
-        <v>96.7</v>
-      </c>
-      <c r="M27">
-        <v>100</v>
-      </c>
       <c r="N27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O27">
         <v>100</v>
       </c>
       <c r="P27">
+        <v>100</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>100</v>
+      </c>
+      <c r="S27">
         <v>93.3</v>
       </c>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:19">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -4977,7 +5205,7 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -4995,7 +5223,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -5012,8 +5240,17 @@
       <c r="P28">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>100</v>
+      </c>
+      <c r="S28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -5027,43 +5264,52 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>96.7</v>
       </c>
       <c r="H29">
+        <v>96.7</v>
+      </c>
+      <c r="I29">
         <v>95</v>
       </c>
-      <c r="I29">
-        <v>100</v>
-      </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L29">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M29">
+        <v>96.7</v>
+      </c>
+      <c r="N29">
+        <v>96.7</v>
+      </c>
+      <c r="O29">
         <v>95</v>
       </c>
-      <c r="N29">
-        <v>100</v>
-      </c>
-      <c r="O29">
-        <v>100</v>
-      </c>
       <c r="P29">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
+        <v>100</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>100</v>
+      </c>
+      <c r="S29">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -5077,16 +5323,16 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>96.7</v>
       </c>
       <c r="H30">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I30">
         <v>100</v>
@@ -5095,25 +5341,34 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O30">
         <v>100</v>
       </c>
       <c r="P30">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
+        <v>100</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>100</v>
+      </c>
+      <c r="S30">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
@@ -5127,7 +5382,7 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -5145,7 +5400,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -5162,8 +5417,17 @@
       <c r="P31">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="1:16">
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>100</v>
+      </c>
+      <c r="S31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -5177,16 +5441,16 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="G32">
         <v>86.7</v>
       </c>
       <c r="H32">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="I32">
         <v>100</v>
@@ -5195,25 +5459,34 @@
         <v>100</v>
       </c>
       <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>100</v>
+      </c>
+      <c r="M32">
         <v>86.7</v>
       </c>
-      <c r="L32">
+      <c r="N32">
         <v>86.7</v>
       </c>
-      <c r="M32">
-        <v>100</v>
-      </c>
-      <c r="N32">
-        <v>100</v>
-      </c>
       <c r="O32">
         <v>100</v>
       </c>
       <c r="P32">
+        <v>100</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>100</v>
+      </c>
+      <c r="S32">
         <v>86.7</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:19">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
@@ -5227,43 +5500,52 @@
         <v>100</v>
       </c>
       <c r="E33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>86.7</v>
       </c>
       <c r="H33">
+        <v>86.7</v>
+      </c>
+      <c r="I33">
         <v>90</v>
       </c>
-      <c r="I33">
-        <v>100</v>
-      </c>
       <c r="J33">
         <v>100</v>
       </c>
       <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>100</v>
+      </c>
+      <c r="M33">
         <v>86.7</v>
       </c>
-      <c r="L33">
+      <c r="N33">
         <v>86.7</v>
       </c>
-      <c r="M33">
+      <c r="O33">
         <v>90</v>
       </c>
-      <c r="N33">
-        <v>100</v>
-      </c>
-      <c r="O33">
-        <v>100</v>
-      </c>
       <c r="P33">
+        <v>100</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>100</v>
+      </c>
+      <c r="S33">
         <v>86.7</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:19">
       <c r="A34" s="1" t="s">
         <v>42</v>
       </c>
@@ -5277,17 +5559,17 @@
         <v>100</v>
       </c>
       <c r="E34">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G34">
+        <v>96.7</v>
+      </c>
+      <c r="H34">
         <v>93.3</v>
       </c>
-      <c r="H34">
-        <v>100</v>
-      </c>
       <c r="I34">
         <v>100</v>
       </c>
@@ -5295,25 +5577,34 @@
         <v>100</v>
       </c>
       <c r="K34">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L34">
+        <v>100</v>
+      </c>
+      <c r="M34">
+        <v>96.7</v>
+      </c>
+      <c r="N34">
         <v>93.3</v>
       </c>
-      <c r="M34">
-        <v>100</v>
-      </c>
-      <c r="N34">
-        <v>100</v>
-      </c>
       <c r="O34">
         <v>100</v>
       </c>
       <c r="P34">
-        <v>96.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16">
+        <v>100</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>100</v>
+      </c>
+      <c r="S34">
+        <v>96.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35" s="1" t="s">
         <v>43</v>
       </c>
@@ -5327,7 +5618,7 @@
         <v>100</v>
       </c>
       <c r="E35">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F35">
         <v>100</v>
@@ -5345,7 +5636,7 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -5362,8 +5653,17 @@
       <c r="P35">
         <v>100</v>
       </c>
-    </row>
-    <row r="36" spans="1:16">
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>100</v>
+      </c>
+      <c r="S35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
       <c r="A36" s="1" t="s">
         <v>44</v>
       </c>
@@ -5377,43 +5677,52 @@
         <v>100</v>
       </c>
       <c r="E36">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="G36">
         <v>86.7</v>
       </c>
       <c r="H36">
+        <v>86.7</v>
+      </c>
+      <c r="I36">
         <v>90</v>
       </c>
-      <c r="I36">
-        <v>100</v>
-      </c>
       <c r="J36">
         <v>100</v>
       </c>
       <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>100</v>
+      </c>
+      <c r="M36">
         <v>86.7</v>
       </c>
-      <c r="L36">
+      <c r="N36">
         <v>86.7</v>
       </c>
-      <c r="M36">
+      <c r="O36">
         <v>90</v>
       </c>
-      <c r="N36">
-        <v>100</v>
-      </c>
-      <c r="O36">
-        <v>100</v>
-      </c>
       <c r="P36">
+        <v>100</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>100</v>
+      </c>
+      <c r="S36">
         <v>86.7</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:19">
       <c r="A37" s="1" t="s">
         <v>45</v>
       </c>
@@ -5427,7 +5736,7 @@
         <v>100</v>
       </c>
       <c r="E37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F37">
         <v>100</v>
@@ -5445,7 +5754,7 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L37">
         <v>100</v>
@@ -5462,8 +5771,17 @@
       <c r="P37">
         <v>100</v>
       </c>
-    </row>
-    <row r="38" spans="1:16">
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>100</v>
+      </c>
+      <c r="S37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19">
       <c r="A38" s="1" t="s">
         <v>46</v>
       </c>
@@ -5477,16 +5795,16 @@
         <v>100</v>
       </c>
       <c r="E38">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G38">
         <v>96.7</v>
       </c>
       <c r="H38">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I38">
         <v>100</v>
@@ -5495,29 +5813,38 @@
         <v>100</v>
       </c>
       <c r="K38">
-        <v>96.7</v>
+        <v>0</v>
       </c>
       <c r="L38">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="M38">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="N38">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O38">
         <v>100</v>
       </c>
       <c r="P38">
+        <v>100</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>100</v>
+      </c>
+      <c r="S38">
         <v>96.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5BLCM - Estadisticos 20231.xlsx
+++ b/grupos/5BLCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="100">
   <si>
     <t>Materia</t>
   </si>
@@ -107,6 +107,9 @@
     <t>MONTALVO PANZO ADAL</t>
   </si>
   <si>
+    <t>MORENO AGUILAR NAHOMY</t>
+  </si>
+  <si>
     <t>OFICIAL VILLASEÑOR MONICA AIME</t>
   </si>
   <si>
@@ -224,268 +227,97 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>MOHENO</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>PALAFOX</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>MONGE</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>GAMBINO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VILLASEÑOR</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>FLOURENS</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
+    <t>YAMILET MONSERRAT</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
   </si>
   <si>
     <t>ANDRES</t>
   </si>
   <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>AXEL EDUARDO</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>EDNA</t>
-  </si>
-  <si>
     <t>CRISTOPHER</t>
   </si>
   <si>
-    <t>LUIS CARLOS</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>DARLA MARLENE</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
-  </si>
-  <si>
     <t>JOSE RAFAEL</t>
   </si>
   <si>
     <t>DIANA CRISTINA</t>
   </si>
   <si>
-    <t>ADAL</t>
-  </si>
-  <si>
-    <t>MARIA SACIRA</t>
-  </si>
-  <si>
-    <t>OLIVA</t>
-  </si>
-  <si>
-    <t>SAIRA LEILANI</t>
-  </si>
-  <si>
-    <t>MONICA AIME</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
   </si>
   <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>GONZALO</t>
-  </si>
-  <si>
-    <t>ROSA JAZMIN</t>
-  </si>
-  <si>
-    <t>REBECA</t>
-  </si>
-  <si>
-    <t>BRIGITTE</t>
-  </si>
-  <si>
     <t>SAYURI BETSABE</t>
   </si>
   <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
     <t>ANA LAURA</t>
   </si>
   <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
     <t>IVANNA DANIELA</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>LIZETH</t>
-  </si>
-  <si>
-    <t>ROSA ITZEL</t>
   </si>
 </sst>
 </file>
@@ -847,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y38"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -984,7 +816,7 @@
         <v>10</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -993,13 +825,13 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1008,7 +840,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1035,10 +867,10 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1061,7 +893,7 @@
         <v>6</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
         <v>6</v>
@@ -1070,13 +902,13 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1085,7 +917,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1112,10 +944,10 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1138,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -1147,13 +979,13 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1162,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1192,7 +1024,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1215,7 +1047,7 @@
         <v>6</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1224,13 +1056,13 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1239,7 +1071,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1266,10 +1098,10 @@
         <v>8</v>
       </c>
       <c r="V7">
+        <v>7</v>
+      </c>
+      <c r="W7">
         <v>6</v>
-      </c>
-      <c r="W7">
-        <v>-1</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1292,7 +1124,7 @@
         <v>9</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -1301,13 +1133,13 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1316,7 +1148,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1337,7 +1169,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1346,13 +1178,13 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X8">
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1369,7 +1201,7 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -1378,13 +1210,13 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1393,7 +1225,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1414,7 +1246,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>10</v>
@@ -1423,13 +1255,13 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>10</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1446,7 +1278,7 @@
         <v>8</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -1455,13 +1287,13 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1470,7 +1302,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1500,7 +1332,7 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1523,7 +1355,7 @@
         <v>7</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>8</v>
@@ -1532,13 +1364,13 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1547,7 +1379,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1568,7 +1400,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1577,13 +1409,13 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X11">
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1600,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F12">
         <v>8</v>
@@ -1609,13 +1441,13 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1624,7 +1456,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1654,7 +1486,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1677,7 +1509,7 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>9</v>
@@ -1686,13 +1518,13 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1701,7 +1533,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1731,7 +1563,7 @@
         <v>5</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1754,7 +1586,7 @@
         <v>8</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F14">
         <v>10</v>
@@ -1763,13 +1595,13 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1778,7 +1610,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1808,7 +1640,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1831,7 +1663,7 @@
         <v>8</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -1840,13 +1672,13 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1855,7 +1687,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1882,10 +1714,10 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1908,7 +1740,7 @@
         <v>9</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F16">
         <v>6</v>
@@ -1917,13 +1749,13 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1932,7 +1764,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1959,10 +1791,10 @@
         <v>9</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1985,7 +1817,7 @@
         <v>8</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F17">
         <v>8</v>
@@ -1994,13 +1826,13 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2009,7 +1841,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2036,10 +1868,10 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2062,7 +1894,7 @@
         <v>10</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>10</v>
@@ -2071,13 +1903,13 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2086,7 +1918,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2116,7 +1948,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2139,7 +1971,7 @@
         <v>8</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F19">
         <v>10</v>
@@ -2148,13 +1980,13 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2163,7 +1995,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2184,7 +2016,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>9</v>
@@ -2193,7 +2025,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>10</v>
@@ -2216,7 +2048,7 @@
         <v>8</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F20">
         <v>8</v>
@@ -2225,13 +2057,13 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2240,7 +2072,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2270,7 +2102,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X20">
         <v>8</v>
@@ -2284,76 +2116,76 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F21">
+        <v>-1</v>
+      </c>
+      <c r="G21">
+        <v>7</v>
+      </c>
+      <c r="H21">
+        <v>6</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+      <c r="J21">
+        <v>6</v>
+      </c>
+      <c r="K21">
+        <v>-1</v>
+      </c>
+      <c r="L21">
+        <v>-1</v>
+      </c>
+      <c r="M21">
+        <v>6</v>
+      </c>
+      <c r="N21">
+        <v>-1</v>
+      </c>
+      <c r="O21">
+        <v>-1</v>
+      </c>
+      <c r="P21">
+        <v>-1</v>
+      </c>
+      <c r="Q21">
+        <v>-1</v>
+      </c>
+      <c r="R21">
+        <v>-1</v>
+      </c>
+      <c r="S21">
+        <v>-1</v>
+      </c>
+      <c r="T21">
+        <v>7</v>
+      </c>
+      <c r="U21">
+        <v>10</v>
+      </c>
+      <c r="V21">
+        <v>6</v>
+      </c>
+      <c r="W21">
         <v>5</v>
       </c>
-      <c r="G21">
-        <v>8</v>
-      </c>
-      <c r="H21">
-        <v>-1</v>
-      </c>
-      <c r="I21">
-        <v>-1</v>
-      </c>
-      <c r="J21">
-        <v>-1</v>
-      </c>
-      <c r="K21">
-        <v>-1</v>
-      </c>
-      <c r="L21">
-        <v>-1</v>
-      </c>
-      <c r="M21">
-        <v>-1</v>
-      </c>
-      <c r="N21">
-        <v>-1</v>
-      </c>
-      <c r="O21">
-        <v>-1</v>
-      </c>
-      <c r="P21">
-        <v>-1</v>
-      </c>
-      <c r="Q21">
-        <v>-1</v>
-      </c>
-      <c r="R21">
-        <v>-1</v>
-      </c>
-      <c r="S21">
-        <v>-1</v>
-      </c>
-      <c r="T21">
-        <v>8</v>
-      </c>
-      <c r="U21">
-        <v>8</v>
-      </c>
-      <c r="V21">
-        <v>5</v>
-      </c>
-      <c r="W21">
-        <v>-1</v>
-      </c>
       <c r="X21">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2361,31 +2193,31 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2394,7 +2226,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2415,22 +2247,22 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2441,28 +2273,28 @@
         <v>10</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23">
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2471,7 +2303,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2495,16 +2327,16 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y23">
         <v>10</v>
@@ -2515,7 +2347,7 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C24">
         <v>10</v>
@@ -2524,22 +2356,22 @@
         <v>7</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2548,7 +2380,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2569,7 +2401,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2578,13 +2410,13 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2592,31 +2424,31 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25">
         <v>10</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>10</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2625,7 +2457,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2652,10 +2484,10 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2675,10 +2507,10 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F26">
         <v>10</v>
@@ -2687,13 +2519,13 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2702,7 +2534,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2729,10 +2561,10 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2746,31 +2578,31 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2779,7 +2611,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2800,22 +2632,22 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2823,31 +2655,31 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -2856,7 +2688,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2880,16 +2712,16 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2900,31 +2732,31 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29">
         <v>10</v>
       </c>
       <c r="D29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -2933,7 +2765,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2954,22 +2786,22 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>10</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2977,31 +2809,31 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -3010,7 +2842,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3034,16 +2866,16 @@
         <v>10</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>8</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -3057,28 +2889,28 @@
         <v>10</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31">
         <v>8</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G31">
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -3087,7 +2919,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3111,16 +2943,16 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>8</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -3131,31 +2963,31 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3164,7 +2996,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3185,22 +3017,22 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3217,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F33">
         <v>8</v>
@@ -3226,13 +3058,13 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -3241,7 +3073,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3262,7 +3094,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>7</v>
@@ -3271,13 +3103,13 @@
         <v>5</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X33">
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3285,32 +3117,32 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F34">
+        <v>8</v>
+      </c>
+      <c r="G34">
+        <v>8</v>
+      </c>
+      <c r="H34">
+        <v>7</v>
+      </c>
+      <c r="I34">
+        <v>7</v>
+      </c>
+      <c r="J34">
         <v>6</v>
       </c>
-      <c r="G34">
-        <v>10</v>
-      </c>
-      <c r="H34">
-        <v>-1</v>
-      </c>
-      <c r="I34">
-        <v>-1</v>
-      </c>
-      <c r="J34">
-        <v>-1</v>
-      </c>
       <c r="K34">
         <v>-1</v>
       </c>
@@ -3318,7 +3150,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3339,22 +3171,22 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>5</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3362,31 +3194,31 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G35">
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3395,7 +3227,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3419,16 +3251,16 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3439,31 +3271,31 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3472,7 +3304,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3493,22 +3325,22 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U36">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3516,31 +3348,31 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -3549,7 +3381,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3570,22 +3402,22 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3602,22 +3434,22 @@
         <v>8</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F38">
         <v>10</v>
       </c>
       <c r="G38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -3626,7 +3458,7 @@
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3656,13 +3488,90 @@
         <v>8</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X38">
         <v>10</v>
       </c>
       <c r="Y38">
-        <v>9</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25">
+      <c r="A39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39">
+        <v>10</v>
+      </c>
+      <c r="C39">
+        <v>10</v>
+      </c>
+      <c r="D39">
+        <v>8</v>
+      </c>
+      <c r="E39">
+        <v>6</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
+      </c>
+      <c r="G39">
+        <v>9</v>
+      </c>
+      <c r="H39">
+        <v>10</v>
+      </c>
+      <c r="I39">
+        <v>10</v>
+      </c>
+      <c r="J39">
+        <v>6</v>
+      </c>
+      <c r="K39">
+        <v>-1</v>
+      </c>
+      <c r="L39">
+        <v>-1</v>
+      </c>
+      <c r="M39">
+        <v>10</v>
+      </c>
+      <c r="N39">
+        <v>-1</v>
+      </c>
+      <c r="O39">
+        <v>-1</v>
+      </c>
+      <c r="P39">
+        <v>-1</v>
+      </c>
+      <c r="Q39">
+        <v>-1</v>
+      </c>
+      <c r="R39">
+        <v>-1</v>
+      </c>
+      <c r="S39">
+        <v>-1</v>
+      </c>
+      <c r="T39">
+        <v>10</v>
+      </c>
+      <c r="U39">
+        <v>10</v>
+      </c>
+      <c r="V39">
+        <v>7</v>
+      </c>
+      <c r="W39">
+        <v>6</v>
+      </c>
+      <c r="X39">
+        <v>10</v>
+      </c>
+      <c r="Y39">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3678,7 +3587,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -3687,7 +3596,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3695,7 +3604,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -3703,7 +3612,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -3789,7 +3698,7 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -3798,7 +3707,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -3807,16 +3716,16 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>100</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3825,13 +3734,13 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
         <v>100</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3848,7 +3757,7 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -3857,7 +3766,7 @@
         <v>96.7</v>
       </c>
       <c r="H5">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I5">
         <v>100</v>
@@ -3866,16 +3775,16 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>96.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N5">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -3884,13 +3793,13 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>96.7</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3907,7 +3816,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -3916,7 +3825,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I6">
         <v>100</v>
@@ -3925,7 +3834,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3934,7 +3843,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -3943,7 +3852,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -3966,7 +3875,7 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -3975,7 +3884,7 @@
         <v>96.7</v>
       </c>
       <c r="H7">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I7">
         <v>95</v>
@@ -3984,16 +3893,16 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
-        <v>96.7</v>
+        <v>95.5</v>
       </c>
       <c r="N7">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O7">
         <v>95</v>
@@ -4002,13 +3911,13 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
         <v>100</v>
       </c>
       <c r="S7">
-        <v>96.7</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4025,7 +3934,7 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -4034,7 +3943,7 @@
         <v>86.7</v>
       </c>
       <c r="H8">
-        <v>86.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -4043,16 +3952,16 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>86.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="N8">
-        <v>86.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -4061,13 +3970,13 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>86.7</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4084,7 +3993,7 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -4093,7 +4002,7 @@
         <v>96.7</v>
       </c>
       <c r="H9">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="I9">
         <v>100</v>
@@ -4102,16 +4011,16 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>100</v>
       </c>
       <c r="M9">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="N9">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -4120,13 +4029,13 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
         <v>100</v>
       </c>
       <c r="S9">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4143,7 +4052,7 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -4161,7 +4070,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -4179,7 +4088,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -4202,7 +4111,7 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -4211,40 +4120,40 @@
         <v>96.7</v>
       </c>
       <c r="H11">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I11">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>96.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N11">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="O11">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
         <v>100</v>
       </c>
       <c r="S11">
-        <v>96.7</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4261,7 +4170,7 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -4279,7 +4188,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -4297,7 +4206,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -4320,7 +4229,7 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -4329,7 +4238,7 @@
         <v>96.7</v>
       </c>
       <c r="H13">
-        <v>96.7</v>
+        <v>95.5</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -4338,16 +4247,16 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
-        <v>96.7</v>
+        <v>95.5</v>
       </c>
       <c r="N13">
-        <v>96.7</v>
+        <v>95.5</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -4356,13 +4265,13 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>96.7</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4379,7 +4288,7 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -4388,7 +4297,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -4397,16 +4306,16 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>100</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -4415,13 +4324,13 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4438,7 +4347,7 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -4447,7 +4356,7 @@
         <v>96.7</v>
       </c>
       <c r="H15">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="I15">
         <v>100</v>
@@ -4456,16 +4365,16 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="N15">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -4474,13 +4383,13 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
         <v>100</v>
       </c>
       <c r="S15">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4497,7 +4406,7 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -4515,7 +4424,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -4533,7 +4442,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -4556,7 +4465,7 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -4565,7 +4474,7 @@
         <v>96.7</v>
       </c>
       <c r="H17">
-        <v>96.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I17">
         <v>95</v>
@@ -4574,16 +4483,16 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
-        <v>96.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N17">
-        <v>96.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O17">
         <v>95</v>
@@ -4592,13 +4501,13 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
         <v>100</v>
       </c>
       <c r="S17">
-        <v>96.7</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4615,7 +4524,7 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -4624,7 +4533,7 @@
         <v>93.3</v>
       </c>
       <c r="H18">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="I18">
         <v>95</v>
@@ -4633,16 +4542,16 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
       <c r="N18">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="O18">
         <v>95</v>
@@ -4651,13 +4560,13 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="S18">
-        <v>93.3</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4674,7 +4583,7 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -4683,7 +4592,7 @@
         <v>93.3</v>
       </c>
       <c r="H19">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -4692,16 +4601,16 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>93.3</v>
+        <v>97</v>
       </c>
       <c r="N19">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -4710,13 +4619,13 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
         <v>100</v>
       </c>
       <c r="S19">
-        <v>93.3</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4733,7 +4642,7 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -4742,7 +4651,7 @@
         <v>96.7</v>
       </c>
       <c r="H20">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="I20">
         <v>100</v>
@@ -4751,16 +4660,16 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>100</v>
       </c>
       <c r="M20">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="N20">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -4769,13 +4678,13 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
         <v>100</v>
       </c>
       <c r="S20">
-        <v>96.7</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4783,58 +4692,58 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="C21">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>100</v>
       </c>
       <c r="E21">
+        <v>100</v>
+      </c>
+      <c r="F21">
         <v>0</v>
-      </c>
-      <c r="F21">
-        <v>100</v>
       </c>
       <c r="G21">
         <v>90</v>
       </c>
       <c r="H21">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I21">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
+        <v>100</v>
+      </c>
+      <c r="L21">
         <v>0</v>
       </c>
-      <c r="L21">
-        <v>100</v>
-      </c>
       <c r="M21">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="N21">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="O21">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
+        <v>100</v>
+      </c>
+      <c r="R21">
         <v>0</v>
       </c>
-      <c r="R21">
-        <v>100</v>
-      </c>
       <c r="S21">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4842,58 +4751,58 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="C22">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D22">
         <v>100</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>100</v>
       </c>
       <c r="G22">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H22">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I22">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>100</v>
       </c>
       <c r="M22">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N22">
-        <v>93.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O22">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P22">
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
         <v>100</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4901,7 +4810,7 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -4910,16 +4819,16 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>100</v>
       </c>
       <c r="G23">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H23">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="I23">
         <v>100</v>
@@ -4928,16 +4837,16 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="N23">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -4946,13 +4855,13 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>96.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4969,16 +4878,16 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>100</v>
       </c>
       <c r="G24">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="H24">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="I24">
         <v>100</v>
@@ -4987,16 +4896,16 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24">
-        <v>93.3</v>
+        <v>98.5</v>
       </c>
       <c r="N24">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -5005,13 +4914,13 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
         <v>100</v>
       </c>
       <c r="S24">
-        <v>93.3</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5028,16 +4937,16 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>100</v>
       </c>
       <c r="G25">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="H25">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="I25">
         <v>100</v>
@@ -5046,16 +4955,16 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>100</v>
       </c>
       <c r="M25">
-        <v>96.7</v>
+        <v>97</v>
       </c>
       <c r="N25">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -5064,13 +4973,13 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
         <v>100</v>
       </c>
       <c r="S25">
-        <v>96.7</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5078,7 +4987,7 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -5087,16 +4996,16 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>100</v>
       </c>
       <c r="G26">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H26">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I26">
         <v>100</v>
@@ -5105,16 +5014,16 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N26">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -5123,13 +5032,13 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5137,7 +5046,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -5146,16 +5055,16 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>100</v>
       </c>
       <c r="G27">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="H27">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -5164,16 +5073,16 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="N27">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -5182,13 +5091,13 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>93.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5196,7 +5105,7 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="C28">
         <v>100</v>
@@ -5205,16 +5114,16 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>100</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="H28">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="I28">
         <v>100</v>
@@ -5223,16 +5132,16 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>100</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N28">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -5241,13 +5150,13 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
         <v>100</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5255,58 +5164,58 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="C29">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>100</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>100</v>
       </c>
       <c r="G29">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H29">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="I29">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J29">
         <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="N29">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="O29">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="P29">
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
         <v>100</v>
       </c>
       <c r="S29">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5317,13 +5226,13 @@
         <v>96.7</v>
       </c>
       <c r="C30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D30">
         <v>100</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -5332,40 +5241,40 @@
         <v>96.7</v>
       </c>
       <c r="H30">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J30">
         <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>100</v>
       </c>
       <c r="M30">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="N30">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P30">
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
         <v>100</v>
       </c>
       <c r="S30">
-        <v>96.7</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5373,7 +5282,7 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="C31">
         <v>100</v>
@@ -5382,16 +5291,16 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>100</v>
       </c>
       <c r="G31">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H31">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="I31">
         <v>100</v>
@@ -5400,16 +5309,16 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="O31">
         <v>100</v>
@@ -5418,13 +5327,13 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
         <v>100</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5432,7 +5341,7 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>100</v>
@@ -5441,16 +5350,16 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>100</v>
       </c>
       <c r="G32">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="H32">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="I32">
         <v>100</v>
@@ -5459,16 +5368,16 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>100</v>
       </c>
       <c r="M32">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="N32">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="O32">
         <v>100</v>
@@ -5477,13 +5386,13 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="S32">
-        <v>86.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5494,13 +5403,13 @@
         <v>86.7</v>
       </c>
       <c r="C33">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>100</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -5509,40 +5418,40 @@
         <v>86.7</v>
       </c>
       <c r="H33">
-        <v>86.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I33">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J33">
         <v>100</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>100</v>
       </c>
       <c r="M33">
-        <v>86.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="N33">
-        <v>86.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O33">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P33">
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
         <v>100</v>
       </c>
       <c r="S33">
-        <v>86.7</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5550,58 +5459,58 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="C34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D34">
         <v>100</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34">
         <v>100</v>
       </c>
       <c r="G34">
-        <v>96.7</v>
+        <v>86.7</v>
       </c>
       <c r="H34">
-        <v>93.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
         <v>100</v>
       </c>
       <c r="M34">
-        <v>96.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="N34">
-        <v>93.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O34">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P34">
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34">
         <v>100</v>
       </c>
       <c r="S34">
-        <v>96.7</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5609,7 +5518,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="C35">
         <v>100</v>
@@ -5618,16 +5527,16 @@
         <v>100</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35">
         <v>100</v>
       </c>
       <c r="G35">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H35">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I35">
         <v>100</v>
@@ -5636,16 +5545,16 @@
         <v>100</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35">
         <v>100</v>
       </c>
       <c r="M35">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="N35">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="O35">
         <v>100</v>
@@ -5654,13 +5563,13 @@
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35">
         <v>100</v>
       </c>
       <c r="S35">
-        <v>100</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5668,58 +5577,58 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="C36">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>100</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F36">
         <v>100</v>
       </c>
       <c r="G36">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="H36">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="I36">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J36">
         <v>100</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36">
         <v>100</v>
       </c>
       <c r="M36">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="N36">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="O36">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="P36">
         <v>100</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R36">
         <v>100</v>
       </c>
       <c r="S36">
-        <v>86.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5727,58 +5636,58 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="C37">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D37">
         <v>100</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37">
         <v>100</v>
       </c>
       <c r="G37">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="H37">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I37">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J37">
         <v>100</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L37">
         <v>100</v>
       </c>
       <c r="M37">
-        <v>100</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="N37">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O37">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P37">
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R37">
         <v>100</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5786,58 +5695,117 @@
         <v>46</v>
       </c>
       <c r="B38">
+        <v>100</v>
+      </c>
+      <c r="C38">
+        <v>100</v>
+      </c>
+      <c r="D38">
+        <v>100</v>
+      </c>
+      <c r="E38">
+        <v>100</v>
+      </c>
+      <c r="F38">
+        <v>100</v>
+      </c>
+      <c r="G38">
+        <v>100</v>
+      </c>
+      <c r="H38">
+        <v>97</v>
+      </c>
+      <c r="I38">
+        <v>100</v>
+      </c>
+      <c r="J38">
+        <v>100</v>
+      </c>
+      <c r="K38">
+        <v>100</v>
+      </c>
+      <c r="L38">
+        <v>100</v>
+      </c>
+      <c r="M38">
+        <v>97</v>
+      </c>
+      <c r="N38">
+        <v>97</v>
+      </c>
+      <c r="O38">
+        <v>100</v>
+      </c>
+      <c r="P38">
+        <v>100</v>
+      </c>
+      <c r="Q38">
+        <v>100</v>
+      </c>
+      <c r="R38">
+        <v>100</v>
+      </c>
+      <c r="S38">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39">
         <v>96.7</v>
       </c>
-      <c r="C38">
-        <v>100</v>
-      </c>
-      <c r="D38">
-        <v>100</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>100</v>
-      </c>
-      <c r="G38">
+      <c r="C39">
+        <v>100</v>
+      </c>
+      <c r="D39">
+        <v>100</v>
+      </c>
+      <c r="E39">
+        <v>100</v>
+      </c>
+      <c r="F39">
+        <v>100</v>
+      </c>
+      <c r="G39">
         <v>96.7</v>
       </c>
-      <c r="H38">
-        <v>96.7</v>
-      </c>
-      <c r="I38">
-        <v>100</v>
-      </c>
-      <c r="J38">
-        <v>100</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>100</v>
-      </c>
-      <c r="M38">
-        <v>96.7</v>
-      </c>
-      <c r="N38">
-        <v>96.7</v>
-      </c>
-      <c r="O38">
-        <v>100</v>
-      </c>
-      <c r="P38">
-        <v>100</v>
-      </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38">
-        <v>100</v>
-      </c>
-      <c r="S38">
-        <v>96.7</v>
+      <c r="H39">
+        <v>98.5</v>
+      </c>
+      <c r="I39">
+        <v>100</v>
+      </c>
+      <c r="J39">
+        <v>100</v>
+      </c>
+      <c r="K39">
+        <v>100</v>
+      </c>
+      <c r="L39">
+        <v>100</v>
+      </c>
+      <c r="M39">
+        <v>97</v>
+      </c>
+      <c r="N39">
+        <v>98.5</v>
+      </c>
+      <c r="O39">
+        <v>100</v>
+      </c>
+      <c r="P39">
+        <v>100</v>
+      </c>
+      <c r="Q39">
+        <v>100</v>
+      </c>
+      <c r="R39">
+        <v>100</v>
+      </c>
+      <c r="S39">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5865,31 +5833,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -5897,28 +5865,31 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2">
+        <v>25</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="G2" s="2">
+        <v>30.6</v>
+      </c>
+      <c r="H2">
+        <v>6.2</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>35</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5926,25 +5897,25 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E3">
         <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>82.90000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="G3" s="2">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5958,10 +5929,10 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4">
         <v>33</v>
@@ -5970,19 +5941,19 @@
         <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>94.3</v>
+        <v>91.7</v>
       </c>
       <c r="G4" s="2">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H4">
         <v>8.6</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5990,13 +5961,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6022,13 +5993,13 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6040,7 +6011,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6054,13 +6025,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6072,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6088,7 +6059,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6097,16 +6068,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6117,702 +6088,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920289</v>
+        <v>19330051920208</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920290</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920291</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" t="s">
-        <v>124</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920292</v>
-      </c>
-      <c r="B5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920293</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920295</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920297</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920337</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920301</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" t="s">
-        <v>130</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920302</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" t="s">
-        <v>131</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920304</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920306</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D13" t="s">
-        <v>133</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920235</v>
-      </c>
-      <c r="B14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920307</v>
-      </c>
-      <c r="B15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" t="s">
-        <v>135</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920309</v>
-      </c>
-      <c r="B16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" t="s">
-        <v>136</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051130222</v>
-      </c>
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" t="s">
-        <v>137</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920090</v>
-      </c>
-      <c r="B18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" t="s">
-        <v>138</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920310</v>
-      </c>
-      <c r="B19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19" t="s">
-        <v>139</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920311</v>
-      </c>
-      <c r="B20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C20" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" t="s">
-        <v>140</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920313</v>
-      </c>
-      <c r="B21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" t="s">
-        <v>141</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920314</v>
-      </c>
-      <c r="B22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" t="s">
-        <v>111</v>
-      </c>
-      <c r="D22" t="s">
-        <v>142</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920172</v>
-      </c>
-      <c r="B23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" t="s">
-        <v>143</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920315</v>
-      </c>
-      <c r="B24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920316</v>
-      </c>
-      <c r="B25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" t="s">
-        <v>114</v>
-      </c>
-      <c r="D25" t="s">
-        <v>141</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920317</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920318</v>
-      </c>
-      <c r="B27" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" t="s">
-        <v>116</v>
-      </c>
-      <c r="D27" t="s">
-        <v>146</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920319</v>
-      </c>
-      <c r="B28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" t="s">
-        <v>147</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920320</v>
-      </c>
-      <c r="B29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" t="s">
-        <v>117</v>
-      </c>
-      <c r="D29" t="s">
-        <v>148</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920321</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" t="s">
-        <v>149</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920323</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920326</v>
-      </c>
-      <c r="B32" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" t="s">
-        <v>151</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920327</v>
-      </c>
-      <c r="B33" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" t="s">
-        <v>79</v>
-      </c>
-      <c r="D33" t="s">
-        <v>152</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920328</v>
-      </c>
-      <c r="B34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C34" t="s">
-        <v>119</v>
-      </c>
-      <c r="D34" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920329</v>
-      </c>
-      <c r="B35" t="s">
-        <v>97</v>
-      </c>
-      <c r="C35" t="s">
-        <v>120</v>
-      </c>
-      <c r="D35" t="s">
-        <v>154</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920330</v>
-      </c>
-      <c r="B36" t="s">
-        <v>98</v>
-      </c>
-      <c r="C36" t="s">
-        <v>121</v>
-      </c>
-      <c r="D36" t="s">
-        <v>155</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -6822,7 +6113,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6831,22 +6122,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -6857,19 +6148,19 @@
         <v>21330051920302</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6880,39 +6171,39 @@
         <v>21330051920302</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920321</v>
+        <v>19330051920208</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>60</v>
@@ -6923,22 +6214,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920321</v>
+        <v>19330051920208</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6949,19 +6240,19 @@
         <v>21330051920323</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6972,39 +6263,39 @@
         <v>21330051920323</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920326</v>
+        <v>21330051920289</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>60</v>
@@ -7015,692 +6306,163 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920326</v>
+        <v>21330051920337</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>151</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920289</v>
+        <v>20330051920235</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920290</v>
+        <v>21330051920307</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920291</v>
+        <v>21330051920316</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920292</v>
+        <v>21330051920319</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920293</v>
+        <v>21330051920321</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920295</v>
+        <v>21330051920326</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920297</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920337</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920301</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" t="s">
-        <v>130</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920304</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920306</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" t="s">
-        <v>133</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920235</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" t="s">
-        <v>134</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920307</v>
-      </c>
-      <c r="B22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920309</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>85</v>
-      </c>
-      <c r="D23" t="s">
-        <v>136</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>59</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051130222</v>
-      </c>
-      <c r="B24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920090</v>
-      </c>
-      <c r="B25" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>59</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920310</v>
-      </c>
-      <c r="B26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920313</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" t="s">
-        <v>141</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>59</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920314</v>
-      </c>
-      <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>142</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920172</v>
-      </c>
-      <c r="B29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" t="s">
-        <v>143</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>59</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920315</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30" t="s">
-        <v>144</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>59</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920316</v>
-      </c>
-      <c r="B31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>59</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920317</v>
-      </c>
-      <c r="B32" t="s">
-        <v>90</v>
-      </c>
-      <c r="C32" t="s">
-        <v>115</v>
-      </c>
-      <c r="D32" t="s">
-        <v>145</v>
-      </c>
-      <c r="E32" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920318</v>
-      </c>
-      <c r="B33" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" t="s">
-        <v>116</v>
-      </c>
-      <c r="D33" t="s">
-        <v>146</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920319</v>
-      </c>
-      <c r="B34" t="s">
-        <v>91</v>
-      </c>
-      <c r="C34" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" t="s">
-        <v>147</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>59</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920320</v>
-      </c>
-      <c r="B35" t="s">
-        <v>92</v>
-      </c>
-      <c r="C35" t="s">
-        <v>117</v>
-      </c>
-      <c r="D35" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>59</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920327</v>
-      </c>
-      <c r="B36" t="s">
-        <v>95</v>
-      </c>
-      <c r="C36" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" t="s">
-        <v>152</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920329</v>
-      </c>
-      <c r="B37" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" t="s">
-        <v>120</v>
-      </c>
-      <c r="D37" t="s">
-        <v>154</v>
-      </c>
-      <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>59</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920330</v>
-      </c>
-      <c r="B38" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38" t="s">
-        <v>121</v>
-      </c>
-      <c r="D38" t="s">
-        <v>155</v>
-      </c>
-      <c r="E38" t="s">
-        <v>8</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5BLCM - Estadisticos 20231.xlsx
+++ b/grupos/5BLCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -227,91 +227,85 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MORENO</t>
   </si>
   <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>YAMILET MONSERRAT</t>
+  </si>
+  <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
     <t>NAHOMY</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
     <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>SAYURI BETSABE</t>
   </si>
   <si>
     <t>ANA LAURA</t>
@@ -834,10 +828,10 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>9</v>
@@ -870,7 +864,7 @@
         <v>9</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -911,10 +905,10 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>8</v>
@@ -950,7 +944,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>9</v>
@@ -988,10 +982,10 @@
         <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -1024,7 +1018,7 @@
         <v>8</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1065,10 +1059,10 @@
         <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -1104,7 +1098,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1142,10 +1136,10 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1181,7 +1175,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1219,10 +1213,10 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -1255,7 +1249,7 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1296,10 +1290,10 @@
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1332,7 +1326,7 @@
         <v>8</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1373,10 +1367,10 @@
         <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>7</v>
@@ -1412,7 +1406,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1450,10 +1444,10 @@
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1486,7 +1480,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1527,10 +1521,10 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1563,7 +1557,7 @@
         <v>5</v>
       </c>
       <c r="W13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1604,10 +1598,10 @@
         <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>9</v>
@@ -1681,10 +1675,10 @@
         <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>9</v>
@@ -1717,7 +1711,7 @@
         <v>7</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1758,10 +1752,10 @@
         <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -1797,7 +1791,7 @@
         <v>5</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1835,10 +1829,10 @@
         <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>9</v>
@@ -1874,7 +1868,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -1912,10 +1906,10 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -1948,7 +1942,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -1989,10 +1983,10 @@
         <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>10</v>
@@ -2025,7 +2019,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>10</v>
@@ -2066,10 +2060,10 @@
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2102,10 +2096,10 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2128,7 +2122,7 @@
         <v>4</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G21">
         <v>7</v>
@@ -2143,10 +2137,10 @@
         <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>6</v>
@@ -2182,7 +2176,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2220,10 +2214,10 @@
         <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>9</v>
@@ -2297,10 +2291,10 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -2333,7 +2327,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2374,10 +2368,10 @@
         <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>10</v>
@@ -2410,10 +2404,10 @@
         <v>7</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2451,10 +2445,10 @@
         <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>10</v>
@@ -2487,7 +2481,7 @@
         <v>7</v>
       </c>
       <c r="W25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2528,10 +2522,10 @@
         <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>9</v>
@@ -2564,7 +2558,7 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2605,10 +2599,10 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>10</v>
@@ -2641,7 +2635,7 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2682,10 +2676,10 @@
         <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>10</v>
@@ -2721,7 +2715,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2759,10 +2753,10 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -2795,7 +2789,7 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2836,10 +2830,10 @@
         <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -2872,10 +2866,10 @@
         <v>8</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -2913,10 +2907,10 @@
         <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>9</v>
@@ -2949,7 +2943,7 @@
         <v>8</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -2990,10 +2984,10 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -3026,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3067,10 +3061,10 @@
         <v>7</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>9</v>
@@ -3103,10 +3097,10 @@
         <v>5</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3144,10 +3138,10 @@
         <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M34">
         <v>7</v>
@@ -3183,7 +3177,7 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3221,10 +3215,10 @@
         <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -3257,10 +3251,10 @@
         <v>5</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3298,10 +3292,10 @@
         <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
         <v>10</v>
@@ -3334,7 +3328,7 @@
         <v>8</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3375,10 +3369,10 @@
         <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>7</v>
@@ -3452,10 +3446,10 @@
         <v>7</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
         <v>10</v>
@@ -3488,7 +3482,7 @@
         <v>8</v>
       </c>
       <c r="W38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>10</v>
@@ -3529,10 +3523,10 @@
         <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M39">
         <v>10</v>
@@ -3701,7 +3695,7 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -3760,7 +3754,7 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G5">
         <v>96.7</v>
@@ -3819,7 +3813,7 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G6">
         <v>100</v>
@@ -3878,7 +3872,7 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G7">
         <v>96.7</v>
@@ -3937,7 +3931,7 @@
         <v>100</v>
       </c>
       <c r="F8">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G8">
         <v>86.7</v>
@@ -3996,7 +3990,7 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G9">
         <v>96.7</v>
@@ -4055,7 +4049,7 @@
         <v>100</v>
       </c>
       <c r="F10">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G10">
         <v>100</v>
@@ -4114,7 +4108,7 @@
         <v>100</v>
       </c>
       <c r="F11">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G11">
         <v>96.7</v>
@@ -4173,7 +4167,7 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G12">
         <v>100</v>
@@ -4232,7 +4226,7 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G13">
         <v>96.7</v>
@@ -4291,7 +4285,7 @@
         <v>100</v>
       </c>
       <c r="F14">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G14">
         <v>100</v>
@@ -4350,7 +4344,7 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G15">
         <v>96.7</v>
@@ -4409,7 +4403,7 @@
         <v>100</v>
       </c>
       <c r="F16">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G16">
         <v>100</v>
@@ -4468,7 +4462,7 @@
         <v>100</v>
       </c>
       <c r="F17">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G17">
         <v>96.7</v>
@@ -4527,7 +4521,7 @@
         <v>100</v>
       </c>
       <c r="F18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G18">
         <v>93.3</v>
@@ -4586,7 +4580,7 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G19">
         <v>93.3</v>
@@ -4645,7 +4639,7 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <v>96.7</v>
@@ -4704,7 +4698,7 @@
         <v>100</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>90</v>
@@ -4719,10 +4713,10 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
         <v>89.40000000000001</v>
@@ -4737,10 +4731,10 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
         <v>89.40000000000001</v>
@@ -4763,7 +4757,7 @@
         <v>100</v>
       </c>
       <c r="F22">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G22">
         <v>90</v>
@@ -4778,10 +4772,10 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="M22">
         <v>95.5</v>
@@ -4796,10 +4790,10 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S22">
         <v>95.5</v>
@@ -4822,7 +4816,7 @@
         <v>100</v>
       </c>
       <c r="F23">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G23">
         <v>100</v>
@@ -4881,7 +4875,7 @@
         <v>100</v>
       </c>
       <c r="F24">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G24">
         <v>96.7</v>
@@ -4940,7 +4934,7 @@
         <v>100</v>
       </c>
       <c r="F25">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G25">
         <v>93.3</v>
@@ -4999,7 +4993,7 @@
         <v>100</v>
       </c>
       <c r="F26">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G26">
         <v>96.7</v>
@@ -5058,7 +5052,7 @@
         <v>100</v>
       </c>
       <c r="F27">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G27">
         <v>100</v>
@@ -5117,7 +5111,7 @@
         <v>100</v>
       </c>
       <c r="F28">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G28">
         <v>93.3</v>
@@ -5176,7 +5170,7 @@
         <v>100</v>
       </c>
       <c r="F29">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G29">
         <v>100</v>
@@ -5235,7 +5229,7 @@
         <v>100</v>
       </c>
       <c r="F30">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G30">
         <v>96.7</v>
@@ -5294,7 +5288,7 @@
         <v>100</v>
       </c>
       <c r="F31">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G31">
         <v>96.7</v>
@@ -5353,7 +5347,7 @@
         <v>100</v>
       </c>
       <c r="F32">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G32">
         <v>100</v>
@@ -5412,7 +5406,7 @@
         <v>100</v>
       </c>
       <c r="F33">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G33">
         <v>86.7</v>
@@ -5471,7 +5465,7 @@
         <v>100</v>
       </c>
       <c r="F34">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G34">
         <v>86.7</v>
@@ -5489,7 +5483,7 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="M34">
         <v>87.90000000000001</v>
@@ -5507,7 +5501,7 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="S34">
         <v>87.90000000000001</v>
@@ -5530,7 +5524,7 @@
         <v>100</v>
       </c>
       <c r="F35">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G35">
         <v>96.7</v>
@@ -5589,7 +5583,7 @@
         <v>100</v>
       </c>
       <c r="F36">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G36">
         <v>100</v>
@@ -5648,7 +5642,7 @@
         <v>100</v>
       </c>
       <c r="F37">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G37">
         <v>86.7</v>
@@ -5663,7 +5657,7 @@
         <v>100</v>
       </c>
       <c r="K37">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="L37">
         <v>100</v>
@@ -5681,7 +5675,7 @@
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="R37">
         <v>100</v>
@@ -5707,7 +5701,7 @@
         <v>100</v>
       </c>
       <c r="F38">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G38">
         <v>100</v>
@@ -5766,7 +5760,7 @@
         <v>100</v>
       </c>
       <c r="F39">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G39">
         <v>96.7</v>
@@ -5871,19 +5865,19 @@
         <v>36</v>
       </c>
       <c r="D2">
+        <v>27</v>
+      </c>
+      <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2">
+        <v>75</v>
+      </c>
+      <c r="G2" s="2">
         <v>25</v>
       </c>
-      <c r="E2">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="G2" s="2">
-        <v>30.6</v>
-      </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5938,22 +5932,22 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
         <v>91.7</v>
       </c>
       <c r="G4" s="2">
-        <v>5.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6059,7 +6053,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6086,26 +6080,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920208</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>62</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6113,7 +6087,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6145,22 +6119,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920302</v>
+        <v>20330051920235</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6168,22 +6142,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920302</v>
+        <v>20330051920235</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6191,22 +6165,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920208</v>
+        <v>21330051920323</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6214,45 +6188,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920208</v>
+        <v>21330051920323</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920323</v>
+        <v>21330051920289</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6260,13 +6234,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920323</v>
+        <v>21330051920337</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
         <v>91</v>
@@ -6283,22 +6257,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920289</v>
+        <v>21330051920302</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
         <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6306,13 +6280,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920337</v>
+        <v>21330051920307</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
         <v>93</v>
@@ -6329,13 +6303,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920235</v>
+        <v>19330051920208</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
         <v>94</v>
@@ -6352,13 +6326,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920307</v>
+        <v>21330051920316</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
         <v>95</v>
@@ -6375,22 +6349,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920316</v>
+        <v>21330051920321</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
         <v>96</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6398,70 +6372,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920319</v>
+        <v>21330051920326</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
         <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920321</v>
-      </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920326</v>
-      </c>
-      <c r="B15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BLCM - Estadisticos 20231.xlsx
+++ b/grupos/5BLCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="95">
   <si>
     <t>Materia</t>
   </si>
@@ -203,15 +203,15 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -230,45 +230,45 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>VILLASEÑOR</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
     <t>ZARATE</t>
   </si>
   <si>
@@ -278,40 +278,31 @@
     <t>MONGE</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>JOSE RAFAEL</t>
   </si>
   <si>
+    <t>MONICA AIME</t>
+  </si>
+  <si>
+    <t>KARINA YOSELIN</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
     <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
   </si>
 </sst>
 </file>
@@ -1500,7 +1491,7 @@
         <v>10</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -1554,7 +1545,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -2193,7 +2184,7 @@
         <v>8</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>4</v>
@@ -2247,7 +2238,7 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>5</v>
@@ -3040,7 +3031,7 @@
         <v>7</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -3094,7 +3085,7 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>7</v>
@@ -3117,7 +3108,7 @@
         <v>7</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E34">
         <v>4</v>
@@ -3171,7 +3162,7 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3194,7 +3185,7 @@
         <v>8</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -3248,7 +3239,7 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W35">
         <v>7</v>
@@ -3348,7 +3339,7 @@
         <v>6</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E37">
         <v>4</v>
@@ -3402,7 +3393,7 @@
         <v>6</v>
       </c>
       <c r="V37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>5</v>
@@ -5888,7 +5879,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -5897,19 +5888,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>83.3</v>
+        <v>91.7</v>
       </c>
       <c r="G3" s="2">
-        <v>16.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5920,7 +5911,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -5929,19 +5920,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5952,7 +5943,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -5973,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6125,10 +6116,10 @@
         <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6148,16 +6139,16 @@
         <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6165,7 +6156,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920323</v>
+        <v>21330051920311</v>
       </c>
       <c r="B4" t="s">
         <v>70</v>
@@ -6174,13 +6165,13 @@
         <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6188,7 +6179,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920323</v>
+        <v>21330051920311</v>
       </c>
       <c r="B5" t="s">
         <v>70</v>
@@ -6197,13 +6188,13 @@
         <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6211,7 +6202,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920289</v>
+        <v>21330051920328</v>
       </c>
       <c r="B6" t="s">
         <v>71</v>
@@ -6220,7 +6211,7 @@
         <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6234,22 +6225,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920337</v>
+        <v>21330051920328</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6257,22 +6248,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920302</v>
+        <v>21330051920289</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6280,16 +6271,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920307</v>
+        <v>21330051920337</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -6303,16 +6294,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920208</v>
+        <v>21330051920307</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -6326,16 +6317,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920316</v>
+        <v>19330051920208</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -6349,22 +6340,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920321</v>
+        <v>21330051920316</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -6372,22 +6363,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920326</v>
+        <v>21330051920323</v>
       </c>
       <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
         <v>78</v>
       </c>
-      <c r="C13" t="s">
-        <v>87</v>
-      </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G13">
         <v>5</v>

--- a/grupos/5BLCM - Estadisticos 20231.xlsx
+++ b/grupos/5BLCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="69">
   <si>
     <t>Materia</t>
   </si>
@@ -200,18 +200,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -225,84 +225,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VILLASEÑOR</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>MONICA AIME</t>
-  </si>
-  <si>
-    <t>KARINA YOSELIN</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
   </si>
 </sst>
 </file>
@@ -828,22 +750,22 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -905,25 +827,25 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -932,13 +854,13 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -982,22 +904,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1059,22 +981,22 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1136,22 +1058,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1163,7 +1085,7 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1213,22 +1135,22 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1290,34 +1212,34 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1367,22 +1289,22 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1394,7 +1316,7 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1444,22 +1366,22 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1521,25 +1443,25 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1548,7 +1470,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1598,22 +1520,22 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1625,7 +1547,7 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1675,22 +1597,22 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1699,10 +1621,10 @@
         <v>9</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1752,37 +1674,37 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1829,22 +1751,22 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -1856,7 +1778,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -1906,22 +1828,22 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -1983,22 +1905,22 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2010,7 +1932,7 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>10</v>
@@ -2060,22 +1982,22 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2087,7 +2009,7 @@
         <v>8</v>
       </c>
       <c r="W20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2137,40 +2059,40 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>10</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2214,37 +2136,37 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>9</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2291,22 +2213,22 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2318,7 +2240,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2368,22 +2290,22 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2392,10 +2314,10 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2445,40 +2367,40 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>10</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2522,40 +2444,40 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>10</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2599,22 +2521,22 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2623,7 +2545,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>8</v>
@@ -2676,25 +2598,25 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>8</v>
@@ -2703,13 +2625,13 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2753,22 +2675,22 @@
         <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2777,10 +2699,10 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2830,22 +2752,22 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -2907,22 +2829,22 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -2937,7 +2859,7 @@
         <v>7</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -2984,22 +2906,22 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3008,10 +2930,10 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3061,22 +2983,22 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -3085,10 +3007,10 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>9</v>
@@ -3138,40 +3060,40 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>7</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3215,25 +3137,25 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -3242,7 +3164,7 @@
         <v>7</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -3292,22 +3214,22 @@
         <v>10</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3369,37 +3291,37 @@
         <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>8</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y37">
         <v>8</v>
@@ -3446,22 +3368,22 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -3523,22 +3445,22 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -3550,10 +3472,10 @@
         <v>7</v>
       </c>
       <c r="W39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -3710,7 +3632,7 @@
         <v>98.5</v>
       </c>
       <c r="N4">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -3725,7 +3647,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3769,10 +3691,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N5">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="O5">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -3784,7 +3706,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3828,7 +3750,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -3887,10 +3809,10 @@
         <v>95.5</v>
       </c>
       <c r="N7">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="O7">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3902,7 +3824,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3946,7 +3868,7 @@
         <v>92.40000000000001</v>
       </c>
       <c r="N8">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -3961,7 +3883,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4005,7 +3927,7 @@
         <v>98.5</v>
       </c>
       <c r="N9">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O9">
         <v>100</v>
@@ -4020,7 +3942,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4067,7 +3989,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -4123,10 +4045,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N11">
-        <v>92.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="O11">
-        <v>92.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P11">
         <v>100</v>
@@ -4138,7 +4060,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>93.90000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4241,7 +4163,7 @@
         <v>95.5</v>
       </c>
       <c r="N13">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -4256,7 +4178,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4300,10 +4222,10 @@
         <v>98.5</v>
       </c>
       <c r="N14">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O14">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -4315,7 +4237,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4359,10 +4281,10 @@
         <v>98.5</v>
       </c>
       <c r="N15">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -4374,7 +4296,7 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>98.5</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4477,10 +4399,10 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N17">
-        <v>93.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="O17">
-        <v>95</v>
+        <v>59.4</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -4492,7 +4414,7 @@
         <v>100</v>
       </c>
       <c r="S17">
-        <v>93.90000000000001</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4536,10 +4458,10 @@
         <v>95.5</v>
       </c>
       <c r="N18">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="O18">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -4551,7 +4473,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>95.5</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4595,7 +4517,7 @@
         <v>97</v>
       </c>
       <c r="N19">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -4610,7 +4532,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4654,7 +4576,7 @@
         <v>97</v>
       </c>
       <c r="N20">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -4669,7 +4591,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4713,7 +4635,7 @@
         <v>89.40000000000001</v>
       </c>
       <c r="N21">
-        <v>89.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -4722,13 +4644,13 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="R21">
         <v>100</v>
       </c>
       <c r="S21">
-        <v>89.40000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4772,22 +4694,22 @@
         <v>95.5</v>
       </c>
       <c r="N22">
-        <v>93.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="O22">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="P22">
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="R22">
-        <v>84.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="S22">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4831,7 +4753,7 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -4846,7 +4768,7 @@
         <v>100</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4890,7 +4812,7 @@
         <v>98.5</v>
       </c>
       <c r="N24">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -4905,7 +4827,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4949,7 +4871,7 @@
         <v>97</v>
       </c>
       <c r="N25">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -4964,7 +4886,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5008,7 +4930,7 @@
         <v>97</v>
       </c>
       <c r="N26">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -5023,7 +4945,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5126,7 +5048,7 @@
         <v>97</v>
       </c>
       <c r="N28">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O28">
         <v>100</v>
@@ -5141,7 +5063,7 @@
         <v>100</v>
       </c>
       <c r="S28">
-        <v>97</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5185,7 +5107,7 @@
         <v>98.5</v>
       </c>
       <c r="N29">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -5200,7 +5122,7 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5244,10 +5166,10 @@
         <v>98.5</v>
       </c>
       <c r="N30">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O30">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -5259,7 +5181,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>98.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5303,7 +5225,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N31">
-        <v>93.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="O31">
         <v>100</v>
@@ -5318,7 +5240,7 @@
         <v>100</v>
       </c>
       <c r="S31">
-        <v>93.90000000000001</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5421,7 +5343,7 @@
         <v>92.40000000000001</v>
       </c>
       <c r="N33">
-        <v>90.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="O33">
         <v>100</v>
@@ -5436,7 +5358,7 @@
         <v>100</v>
       </c>
       <c r="S33">
-        <v>92.40000000000001</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5480,10 +5402,10 @@
         <v>87.90000000000001</v>
       </c>
       <c r="N34">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="O34">
-        <v>90</v>
+        <v>56.3</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -5492,10 +5414,10 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>86.7</v>
+        <v>92</v>
       </c>
       <c r="S34">
-        <v>87.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5539,7 +5461,7 @@
         <v>98.5</v>
       </c>
       <c r="N35">
-        <v>97</v>
+        <v>95.8</v>
       </c>
       <c r="O35">
         <v>100</v>
@@ -5554,7 +5476,7 @@
         <v>100</v>
       </c>
       <c r="S35">
-        <v>98.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5657,22 +5579,22 @@
         <v>87.90000000000001</v>
       </c>
       <c r="N37">
-        <v>90.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="O37">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P37">
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="R37">
         <v>100</v>
       </c>
       <c r="S37">
-        <v>87.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5716,7 +5638,7 @@
         <v>97</v>
       </c>
       <c r="N38">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O38">
         <v>100</v>
@@ -5731,7 +5653,7 @@
         <v>100</v>
       </c>
       <c r="S38">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -5775,10 +5697,10 @@
         <v>97</v>
       </c>
       <c r="N39">
-        <v>98.5</v>
+        <v>99</v>
       </c>
       <c r="O39">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="P39">
         <v>100</v>
@@ -5790,7 +5712,7 @@
         <v>100</v>
       </c>
       <c r="S39">
-        <v>97</v>
+        <v>97.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5847,7 +5769,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>60</v>
@@ -5856,19 +5778,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>8.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5879,7 +5801,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>61</v>
@@ -5888,19 +5810,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5911,7 +5833,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>62</v>
@@ -5932,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5943,7 +5865,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>63</v>
@@ -5996,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6028,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6078,7 +6000,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6108,282 +6030,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>20330051920235</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920235</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920311</v>
-      </c>
-      <c r="B4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920311</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920328</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920328</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920289</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920337</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920307</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920208</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920316</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920323</v>
-      </c>
-      <c r="B13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/5BLCM - Estadisticos 20231.xlsx
+++ b/grupos/5BLCM - Estadisticos 20231.xlsx
@@ -1754,7 +1754,7 @@
         <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -1772,7 +1772,7 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>7</v>
@@ -3063,7 +3063,7 @@
         <v>5</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P34">
         <v>10</v>
@@ -3081,7 +3081,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3448,7 +3448,7 @@
         <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
         <v>6</v>
@@ -4402,7 +4402,7 @@
         <v>94.8</v>
       </c>
       <c r="O17">
-        <v>59.4</v>
+        <v>81.3</v>
       </c>
       <c r="P17">
         <v>100</v>
@@ -5405,7 +5405,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="O34">
-        <v>56.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P34">
         <v>100</v>
@@ -5700,7 +5700,7 @@
         <v>99</v>
       </c>
       <c r="O39">
-        <v>62.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P39">
         <v>100</v>
@@ -5822,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>0</v>

--- a/grupos/5BLCM - Estadisticos 20231.xlsx
+++ b/grupos/5BLCM - Estadisticos 20231.xlsx
@@ -774,10 +774,10 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -845,22 +845,22 @@
         <v>7</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -928,10 +928,10 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -999,22 +999,22 @@
         <v>9</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1076,22 +1076,22 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1159,10 +1159,10 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1233,13 +1233,13 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1307,22 +1307,22 @@
         <v>7</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1387,16 +1387,16 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1461,19 +1461,19 @@
         <v>9</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>10</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1541,13 +1541,13 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1615,22 +1615,22 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1695,16 +1695,16 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1769,22 +1769,22 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1855,7 +1855,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -1926,13 +1926,13 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>10</v>
@@ -2006,13 +2006,13 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2077,22 +2077,22 @@
         <v>10</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>10</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2154,22 +2154,22 @@
         <v>10</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2234,13 +2234,13 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2314,10 +2314,10 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2385,22 +2385,22 @@
         <v>9</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>10</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2462,22 +2462,22 @@
         <v>9</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>10</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2545,10 +2545,10 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2616,22 +2616,22 @@
         <v>9</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2699,10 +2699,10 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2776,10 +2776,10 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -2850,16 +2850,16 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -2930,10 +2930,10 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3001,22 +3001,22 @@
         <v>10</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3078,22 +3078,22 @@
         <v>5</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3155,19 +3155,19 @@
         <v>9</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3238,10 +3238,10 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3309,22 +3309,22 @@
         <v>9</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3392,10 +3392,10 @@
         <v>10</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W38">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X38">
         <v>10</v>
@@ -3469,13 +3469,13 @@
         <v>10</v>
       </c>
       <c r="V39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>10</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5822,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5854,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5886,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5918,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5950,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5BLCM - Estadisticos 20231.xlsx
+++ b/grupos/5BLCM - Estadisticos 20231.xlsx
@@ -774,10 +774,10 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -845,22 +845,22 @@
         <v>7</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -928,10 +928,10 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -999,22 +999,22 @@
         <v>9</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1076,22 +1076,22 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1159,10 +1159,10 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1233,13 +1233,13 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1307,22 +1307,22 @@
         <v>7</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1387,16 +1387,16 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1461,19 +1461,19 @@
         <v>9</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>10</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1541,13 +1541,13 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1615,22 +1615,22 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1695,16 +1695,16 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1769,22 +1769,22 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1855,7 +1855,7 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -1926,13 +1926,13 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>10</v>
@@ -2006,13 +2006,13 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>10</v>
@@ -2077,22 +2077,22 @@
         <v>10</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>10</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2154,22 +2154,22 @@
         <v>10</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2234,13 +2234,13 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2314,10 +2314,10 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2385,22 +2385,22 @@
         <v>9</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>10</v>
       </c>
       <c r="V25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2462,22 +2462,22 @@
         <v>9</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>10</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2545,10 +2545,10 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2616,22 +2616,22 @@
         <v>9</v>
       </c>
       <c r="T28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2699,10 +2699,10 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>10</v>
@@ -2776,10 +2776,10 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -2850,16 +2850,16 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -2930,10 +2930,10 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3001,22 +3001,22 @@
         <v>10</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3078,22 +3078,22 @@
         <v>5</v>
       </c>
       <c r="T34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3155,19 +3155,19 @@
         <v>9</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3238,10 +3238,10 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3309,22 +3309,22 @@
         <v>9</v>
       </c>
       <c r="T37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3392,10 +3392,10 @@
         <v>10</v>
       </c>
       <c r="V38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>10</v>
@@ -3469,13 +3469,13 @@
         <v>10</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5822,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5854,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5886,7 +5886,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5918,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5950,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>
